--- a/data/public/questions_public.xlsx
+++ b/data/public/questions_public.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29029"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_D5042341617B8FA4AD962A89064FA08DCA4CC393" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F67BE00A-8525-4C3F-8339-4D44FD4A5092}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="2472" yWindow="2472" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -24,9 +25,6 @@
     <t>block</t>
   </si>
   <si>
-    <t>id</t>
-  </si>
-  <si>
     <t>full_question</t>
   </si>
   <si>
@@ -91,12 +89,15 @@
   </si>
   <si>
     <t>Какое у Казахстан Темир Жолы фактическое значение по показателю рентабельности среднего задействованного капитала (в %) в 2024 году?</t>
+  </si>
+  <si>
+    <t>question_id</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -148,7 +149,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
@@ -164,9 +165,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Стандартная">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -204,9 +205,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Стандартная">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -241,7 +242,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -276,7 +277,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Стандартная">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -449,36 +450,36 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I16"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.28515625" customWidth="1"/>
+    <col min="1" max="1" width="19.6640625" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
-    <col min="3" max="3" width="85.140625" customWidth="1"/>
-    <col min="4" max="4" width="15.140625" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" customWidth="1"/>
-    <col min="6" max="6" width="24.28515625" customWidth="1"/>
-    <col min="7" max="7" width="22.140625" customWidth="1"/>
-    <col min="8" max="8" width="20.5703125" customWidth="1"/>
-    <col min="9" max="9" width="21.7109375" customWidth="1"/>
+    <col min="3" max="3" width="85.109375" customWidth="1"/>
+    <col min="4" max="4" width="15.109375" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" customWidth="1"/>
+    <col min="6" max="6" width="24.33203125" customWidth="1"/>
+    <col min="7" max="7" width="22.109375" customWidth="1"/>
+    <col min="8" max="8" width="20.5546875" customWidth="1"/>
+    <col min="9" max="9" width="21.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -486,10 +487,10 @@
         <v>0</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
@@ -497,7 +498,7 @@
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -505,41 +506,41 @@
         <v>0</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -547,41 +548,41 @@
         <v>0</v>
       </c>
       <c r="C6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D6" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D7" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D8" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
@@ -589,69 +590,69 @@
         <v>0</v>
       </c>
       <c r="C9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D9" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D10" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C11" t="s">
+        <v>15</v>
+      </c>
+      <c r="D11" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C12" t="s">
         <v>16</v>
       </c>
-      <c r="D11" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12">
-        <v>11</v>
-      </c>
-      <c r="B12" t="s">
-        <v>4</v>
-      </c>
-      <c r="C12" t="s">
-        <v>17</v>
-      </c>
       <c r="D12" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D13" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
@@ -659,13 +660,13 @@
         <v>0</v>
       </c>
       <c r="C14" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D14" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
@@ -673,24 +674,24 @@
         <v>0</v>
       </c>
       <c r="C15" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D15" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D16" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -700,18 +701,18 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/public/questions_public.xlsx
+++ b/data/public/questions_public.xlsx
@@ -1,11 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29029"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_D5042341617B8FA4AD962A89064FA08DCA4CC393" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F67BE00A-8525-4C3F-8339-4D44FD4A5092}"/>
   <bookViews>
-    <workbookView xWindow="2472" yWindow="2472" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -25,6 +24,9 @@
     <t>block</t>
   </si>
   <si>
+    <t>id</t>
+  </si>
+  <si>
     <t>full_question</t>
   </si>
   <si>
@@ -89,15 +91,12 @@
   </si>
   <si>
     <t>Какое у Казахстан Темир Жолы фактическое значение по показателю рентабельности среднего задействованного капитала (в %) в 2024 году?</t>
-  </si>
-  <si>
-    <t>question_id</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -149,7 +148,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
@@ -165,9 +164,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Стандартная">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -205,9 +204,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Стандартная">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -242,7 +241,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -277,7 +276,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Стандартная">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -450,36 +449,36 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I16"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.6640625" customWidth="1"/>
+    <col min="1" max="1" width="5.28515625" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
-    <col min="3" max="3" width="85.109375" customWidth="1"/>
-    <col min="4" max="4" width="15.109375" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" customWidth="1"/>
-    <col min="6" max="6" width="24.33203125" customWidth="1"/>
-    <col min="7" max="7" width="22.109375" customWidth="1"/>
-    <col min="8" max="8" width="20.5546875" customWidth="1"/>
-    <col min="9" max="9" width="21.6640625" customWidth="1"/>
+    <col min="3" max="3" width="85.140625" customWidth="1"/>
+    <col min="4" max="4" width="15.140625" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" customWidth="1"/>
+    <col min="6" max="6" width="24.28515625" customWidth="1"/>
+    <col min="7" max="7" width="22.140625" customWidth="1"/>
+    <col min="8" max="8" width="20.5703125" customWidth="1"/>
+    <col min="9" max="9" width="21.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -487,10 +486,10 @@
         <v>0</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
@@ -498,7 +497,7 @@
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -506,41 +505,41 @@
         <v>0</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -548,41 +547,41 @@
         <v>0</v>
       </c>
       <c r="C6" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C7" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D7" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D8" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -590,69 +589,69 @@
         <v>0</v>
       </c>
       <c r="C9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D9" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D10" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D11" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D12" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D13" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
@@ -660,13 +659,13 @@
         <v>0</v>
       </c>
       <c r="C14" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D14" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
@@ -674,24 +673,24 @@
         <v>0</v>
       </c>
       <c r="C15" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D15" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C16" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D16" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -701,18 +700,18 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
